--- a/surveyProcessing.xlsx
+++ b/surveyProcessing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamilajanmohamed/Library/CloudStorage/Dropbox/Research/ExpenseShocks/data/documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D0787EB-16E0-464A-9076-3B575C281655}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{916FC0BA-C15F-0C4C-B679-DA719F87C806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{57E50125-87C9-E840-AC46-56F2E007DB73}"/>
+    <workbookView xWindow="1240" yWindow="0" windowWidth="27560" windowHeight="18000" xr2:uid="{57E50125-87C9-E840-AC46-56F2E007DB73}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -458,15 +458,6 @@
     <t>What is this??</t>
   </si>
   <si>
-    <t>"21-24"
-"25-34"
-"35-44"
-"45-54"
-"55-64"
-"65+"
-NA: NA/Unknown</t>
-  </si>
-  <si>
     <t>If numeric ~ job_ref, else NA</t>
   </si>
   <si>
@@ -556,17 +547,6 @@
 Likely (75% chance): "I thought it was likely to happen (about 75% chance)",
 Definitely (100% chance)": "I thought it would definitely happen (about 100% chance)"),
 NA: I’m not sure/NA</t>
-  </si>
-  <si>
-    <t>1: "Yes, we could have prevented it or reduced the cost of the expense (for example, with preventive care, maintenance, or insurance)
-2: No, there was nothing we could have done to prevent it or reduce the cost
-NA: NA/I’m not sure</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> any_shock</t>
-  </si>
-  <si>
-    <t>n_ shock</t>
   </si>
   <si>
     <t>lshock_type</t>
@@ -808,6 +788,27 @@
   </si>
   <si>
     <t>Likelihood reported as decimals for values in (0, 1) and as percentages for 0% and 100%. Fomat standardised to decimals i.e. 0.1, … 1.0</t>
+  </si>
+  <si>
+    <t>"- $20k", 
+"$20k-40k",
+ "$40k-60k", 
+  "$60k-80k", 
+"$80k-100k", 
+"$100k-125k", 
+"$125k +
+NA: NA/Unknown</t>
+  </si>
+  <si>
+    <t>1: "Yes, we could have prevented it or reduced the cost of the expense (for example, with preventive care, maintenance, or insurance)
+0: No, there was nothing we could have done to prevent it or reduce the cost
+NA: NA/I’m not sure</t>
+  </si>
+  <si>
+    <t>n_shock</t>
+  </si>
+  <si>
+    <t>any_shock</t>
   </si>
 </sst>
 </file>
@@ -996,6 +997,66 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1003,6 +1064,9 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1010,69 +1074,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1089,10 +1090,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1417,7 +1414,7 @@
   <cols>
     <col min="1" max="1" width="12" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="52" style="3" customWidth="1"/>
-    <col min="3" max="3" width="46.5" style="36" customWidth="1"/>
+    <col min="3" max="3" width="46.5" style="15" customWidth="1"/>
     <col min="4" max="4" width="17.83203125" style="3" customWidth="1"/>
     <col min="5" max="5" width="10.83203125" style="3"/>
     <col min="6" max="6" width="32.5" style="3" customWidth="1"/>
@@ -1426,12 +1423,12 @@
   <sheetData>
     <row r="1" spans="1:7" s="2" customFormat="1" ht="17" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>82</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="11" t="s">
         <v>83</v>
       </c>
       <c r="D1" s="1" t="s">
@@ -1441,29 +1438,29 @@
         <v>89</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A2" s="12" t="s">
-        <v>124</v>
+      <c r="A2" s="32" t="s">
+        <v>123</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="11" t="s">
-        <v>133</v>
-      </c>
-      <c r="D2" s="11"/>
-      <c r="E2" s="11"/>
+      <c r="C2" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="D2" s="31"/>
+      <c r="E2" s="31"/>
       <c r="F2" s="5"/>
     </row>
     <row r="3" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A3" s="12"/>
+      <c r="A3" s="32"/>
       <c r="B3" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="26" t="s">
+      <c r="C3" s="12" t="s">
         <v>86</v>
       </c>
       <c r="D3" s="5" t="s">
@@ -1475,11 +1472,11 @@
       <c r="F3" s="5"/>
     </row>
     <row r="4" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A4" s="12"/>
+      <c r="A4" s="32"/>
       <c r="B4" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="26" t="s">
+      <c r="C4" s="12" t="s">
         <v>92</v>
       </c>
       <c r="D4" s="5" t="s">
@@ -1491,11 +1488,11 @@
       <c r="F4" s="5"/>
     </row>
     <row r="5" spans="1:7" ht="136" x14ac:dyDescent="0.2">
-      <c r="A5" s="12"/>
+      <c r="A5" s="32"/>
       <c r="B5" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="26" t="s">
+      <c r="C5" s="12" t="s">
         <v>109</v>
       </c>
       <c r="D5" s="5" t="s">
@@ -1507,11 +1504,11 @@
       <c r="F5" s="5"/>
     </row>
     <row r="6" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A6" s="12"/>
+      <c r="A6" s="32"/>
       <c r="B6" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="26" t="s">
+      <c r="C6" s="12" t="s">
         <v>93</v>
       </c>
       <c r="D6" s="5" t="s">
@@ -1523,11 +1520,11 @@
       <c r="F6" s="5"/>
     </row>
     <row r="7" spans="1:7" ht="85" x14ac:dyDescent="0.2">
-      <c r="A7" s="12"/>
+      <c r="A7" s="32"/>
       <c r="B7" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="26" t="s">
+      <c r="C7" s="12" t="s">
         <v>110</v>
       </c>
       <c r="D7" s="5" t="s">
@@ -1539,11 +1536,11 @@
       <c r="F7" s="5"/>
     </row>
     <row r="8" spans="1:7" ht="153" x14ac:dyDescent="0.2">
-      <c r="A8" s="12"/>
+      <c r="A8" s="32"/>
       <c r="B8" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="26" t="s">
+      <c r="C8" s="12" t="s">
         <v>111</v>
       </c>
       <c r="D8" s="5" t="s">
@@ -1555,11 +1552,11 @@
       <c r="F8" s="5"/>
     </row>
     <row r="9" spans="1:7" ht="102" x14ac:dyDescent="0.2">
-      <c r="A9" s="12"/>
+      <c r="A9" s="32"/>
       <c r="B9" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="26" t="s">
+      <c r="C9" s="12" t="s">
         <v>112</v>
       </c>
       <c r="D9" s="5" t="s">
@@ -1571,11 +1568,11 @@
       <c r="F9" s="5"/>
     </row>
     <row r="10" spans="1:7" ht="68" x14ac:dyDescent="0.2">
-      <c r="A10" s="12"/>
+      <c r="A10" s="32"/>
       <c r="B10" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="26" t="s">
+      <c r="C10" s="12" t="s">
         <v>113</v>
       </c>
       <c r="D10" s="5" t="s">
@@ -1587,11 +1584,11 @@
       <c r="F10" s="5"/>
     </row>
     <row r="11" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A11" s="12"/>
+      <c r="A11" s="32"/>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="26" t="s">
+      <c r="C11" s="12" t="s">
         <v>98</v>
       </c>
       <c r="D11" s="5" t="s">
@@ -1603,11 +1600,11 @@
       <c r="F11" s="5"/>
     </row>
     <row r="12" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A12" s="12"/>
+      <c r="A12" s="32"/>
       <c r="B12" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C12" s="26" t="s">
+      <c r="C12" s="12" t="s">
         <v>100</v>
       </c>
       <c r="D12" s="5" t="s">
@@ -1618,13 +1615,13 @@
       </c>
       <c r="F12" s="5"/>
     </row>
-    <row r="13" spans="1:7" ht="119" x14ac:dyDescent="0.2">
-      <c r="A13" s="12"/>
+    <row r="13" spans="1:7" ht="136" x14ac:dyDescent="0.2">
+      <c r="A13" s="32"/>
       <c r="B13" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="26" t="s">
-        <v>121</v>
+      <c r="C13" s="12" t="s">
+        <v>209</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>11</v>
@@ -1634,29 +1631,29 @@
       </c>
       <c r="F13" s="5"/>
     </row>
-    <row r="14" spans="1:7" ht="34" x14ac:dyDescent="0.2">
-      <c r="A14" s="12"/>
+    <row r="14" spans="1:7" ht="17" x14ac:dyDescent="0.2">
+      <c r="A14" s="32"/>
       <c r="B14" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="27" t="s">
-        <v>122</v>
+      <c r="C14" s="13" t="s">
+        <v>121</v>
       </c>
       <c r="D14" s="6"/>
       <c r="E14" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="F14" s="6"/>
-      <c r="G14" s="4" t="s">
+      <c r="F14" s="6" t="s">
         <v>120</v>
       </c>
+      <c r="G14" s="4"/>
     </row>
     <row r="15" spans="1:7" ht="119" x14ac:dyDescent="0.2">
-      <c r="A15" s="12"/>
+      <c r="A15" s="32"/>
       <c r="B15" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C15" s="26" t="s">
+      <c r="C15" s="12" t="s">
         <v>114</v>
       </c>
       <c r="D15" s="5" t="s">
@@ -1668,11 +1665,11 @@
       <c r="F15" s="5"/>
     </row>
     <row r="16" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A16" s="12"/>
+      <c r="A16" s="32"/>
       <c r="B16" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="26" t="s">
+      <c r="C16" s="12" t="s">
         <v>101</v>
       </c>
       <c r="D16" s="5" t="s">
@@ -1684,11 +1681,11 @@
       <c r="F16" s="5"/>
     </row>
     <row r="17" spans="1:6" ht="170" x14ac:dyDescent="0.2">
-      <c r="A17" s="12"/>
+      <c r="A17" s="32"/>
       <c r="B17" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="26" t="s">
+      <c r="C17" s="12" t="s">
         <v>115</v>
       </c>
       <c r="D17" s="5" t="s">
@@ -1700,11 +1697,11 @@
       <c r="F17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="85" x14ac:dyDescent="0.2">
-      <c r="A18" s="12"/>
+      <c r="A18" s="32"/>
       <c r="B18" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="C18" s="26" t="s">
+      <c r="C18" s="12" t="s">
         <v>116</v>
       </c>
       <c r="D18" s="5" t="s">
@@ -1716,11 +1713,11 @@
       <c r="F18" s="5"/>
     </row>
     <row r="19" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A19" s="12"/>
+      <c r="A19" s="32"/>
       <c r="B19" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="C19" s="26" t="s">
+      <c r="C19" s="12" t="s">
         <v>97</v>
       </c>
       <c r="D19" s="5" t="s">
@@ -1732,11 +1729,11 @@
       <c r="F19" s="5"/>
     </row>
     <row r="20" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A20" s="12"/>
+      <c r="A20" s="32"/>
       <c r="B20" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C20" s="26" t="s">
+      <c r="C20" s="12" t="s">
         <v>117</v>
       </c>
       <c r="D20" s="5" t="s">
@@ -1746,15 +1743,15 @@
         <v>91</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A21" s="12"/>
+      <c r="A21" s="32"/>
       <c r="B21" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="C21" s="26" t="s">
+      <c r="C21" s="12" t="s">
         <v>118</v>
       </c>
       <c r="D21" s="5" t="s">
@@ -1766,11 +1763,11 @@
       <c r="F21" s="5"/>
     </row>
     <row r="22" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A22" s="12"/>
+      <c r="A22" s="32"/>
       <c r="B22" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C22" s="26" t="s">
+      <c r="C22" s="12" t="s">
         <v>106</v>
       </c>
       <c r="D22" s="5" t="s">
@@ -1782,17 +1779,17 @@
       <c r="F22" s="5"/>
     </row>
     <row r="23" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A23" s="13" t="s">
-        <v>129</v>
+      <c r="A23" s="34" t="s">
+        <v>128</v>
       </c>
       <c r="B23" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="C23" s="28" t="s">
+      <c r="C23" s="14" t="s">
         <v>107</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>144</v>
+        <v>212</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>91</v>
@@ -1800,15 +1797,15 @@
       <c r="F23" s="7"/>
     </row>
     <row r="24" spans="1:6" ht="119" x14ac:dyDescent="0.2">
-      <c r="A24" s="13"/>
+      <c r="A24" s="34"/>
       <c r="B24" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C24" s="28" t="s">
+      <c r="C24" s="14" t="s">
         <v>119</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>145</v>
+        <v>211</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>91</v>
@@ -1816,15 +1813,15 @@
       <c r="F24" s="7"/>
     </row>
     <row r="25" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A25" s="13"/>
+      <c r="A25" s="34"/>
       <c r="B25" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="C25" s="28" t="s">
-        <v>125</v>
+      <c r="C25" s="14" t="s">
+        <v>124</v>
       </c>
       <c r="D25" s="7" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E25" s="7" t="s">
         <v>91</v>
@@ -1832,69 +1829,69 @@
       <c r="F25" s="7"/>
     </row>
     <row r="26" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A26" s="13"/>
+      <c r="A26" s="34"/>
       <c r="B26" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C26" s="28" t="s">
-        <v>126</v>
-      </c>
-      <c r="D26" s="14" t="s">
+      <c r="C26" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="D26" s="35" t="s">
         <v>85</v>
       </c>
-      <c r="E26" s="15"/>
+      <c r="E26" s="36"/>
       <c r="F26" s="7"/>
     </row>
     <row r="27" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A27" s="13"/>
+      <c r="A27" s="34"/>
       <c r="B27" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C27" s="29" t="s">
+      <c r="C27" s="33" t="s">
+        <v>138</v>
+      </c>
+      <c r="D27" s="34" t="s">
+        <v>143</v>
+      </c>
+      <c r="E27" s="34" t="s">
+        <v>95</v>
+      </c>
+      <c r="F27" s="16" t="s">
         <v>139</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>147</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="F27" s="16" t="s">
-        <v>140</v>
-      </c>
     </row>
     <row r="28" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A28" s="13"/>
+      <c r="A28" s="34"/>
       <c r="B28" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C28" s="29"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
+      <c r="C28" s="33"/>
+      <c r="D28" s="34"/>
+      <c r="E28" s="34"/>
       <c r="F28" s="17"/>
     </row>
     <row r="29" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A29" s="13"/>
+      <c r="A29" s="34"/>
       <c r="B29" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C29" s="29"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
+      <c r="C29" s="33"/>
+      <c r="D29" s="34"/>
+      <c r="E29" s="34"/>
       <c r="F29" s="18"/>
     </row>
     <row r="30" spans="1:6" ht="119" x14ac:dyDescent="0.2">
       <c r="A30" s="19" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="C30" s="26" t="s">
-        <v>127</v>
+      <c r="C30" s="12" t="s">
+        <v>126</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>91</v>
@@ -1906,11 +1903,11 @@
       <c r="B31" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C31" s="26" t="s">
-        <v>128</v>
+      <c r="C31" s="12" t="s">
+        <v>127</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="E31" s="5" t="s">
         <v>91</v>
@@ -1922,11 +1919,11 @@
       <c r="B32" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C32" s="26" t="s">
-        <v>131</v>
+      <c r="C32" s="12" t="s">
+        <v>130</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="E32" s="5" t="s">
         <v>108</v>
@@ -1938,11 +1935,11 @@
       <c r="B33" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C33" s="26" t="s">
-        <v>131</v>
+      <c r="C33" s="12" t="s">
+        <v>130</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E33" s="5" t="s">
         <v>108</v>
@@ -1954,11 +1951,11 @@
       <c r="B34" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="C34" s="26" t="s">
-        <v>131</v>
+      <c r="C34" s="12" t="s">
+        <v>130</v>
       </c>
       <c r="D34" s="5" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E34" s="5" t="s">
         <v>108</v>
@@ -1970,11 +1967,11 @@
       <c r="B35" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C35" s="26" t="s">
-        <v>131</v>
+      <c r="C35" s="12" t="s">
+        <v>130</v>
       </c>
       <c r="D35" s="5" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="E35" s="5" t="s">
         <v>108</v>
@@ -1986,11 +1983,11 @@
       <c r="B36" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="C36" s="26" t="s">
-        <v>131</v>
+      <c r="C36" s="12" t="s">
+        <v>130</v>
       </c>
       <c r="D36" s="5" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="E36" s="5" t="s">
         <v>108</v>
@@ -2002,11 +1999,11 @@
       <c r="B37" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="C37" s="26" t="s">
-        <v>131</v>
+      <c r="C37" s="12" t="s">
+        <v>130</v>
       </c>
       <c r="D37" s="5" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="E37" s="5" t="s">
         <v>108</v>
@@ -2018,11 +2015,11 @@
       <c r="B38" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C38" s="26" t="s">
-        <v>131</v>
+      <c r="C38" s="12" t="s">
+        <v>130</v>
       </c>
       <c r="D38" s="5" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E38" s="5" t="s">
         <v>108</v>
@@ -2034,17 +2031,17 @@
       <c r="B39" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="C39" s="26" t="s">
-        <v>131</v>
+      <c r="C39" s="12" t="s">
+        <v>130</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E39" s="5" t="s">
         <v>108</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="40" spans="1:6" ht="51" x14ac:dyDescent="0.2">
@@ -2052,11 +2049,11 @@
       <c r="B40" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C40" s="26" t="s">
-        <v>131</v>
+      <c r="C40" s="12" t="s">
+        <v>130</v>
       </c>
       <c r="D40" s="5" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="E40" s="5" t="s">
         <v>108</v>
@@ -2068,11 +2065,11 @@
       <c r="B41" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="C41" s="26" t="s">
-        <v>131</v>
+      <c r="C41" s="12" t="s">
+        <v>130</v>
       </c>
       <c r="D41" s="5" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="E41" s="5" t="s">
         <v>108</v>
@@ -2084,11 +2081,11 @@
       <c r="B42" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="C42" s="26" t="s">
-        <v>131</v>
+      <c r="C42" s="12" t="s">
+        <v>130</v>
       </c>
       <c r="D42" s="5" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="E42" s="5" t="s">
         <v>108</v>
@@ -2100,11 +2097,11 @@
       <c r="B43" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="C43" s="26" t="s">
-        <v>131</v>
+      <c r="C43" s="12" t="s">
+        <v>130</v>
       </c>
       <c r="D43" s="5" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E43" s="5" t="s">
         <v>108</v>
@@ -2116,11 +2113,11 @@
       <c r="B44" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C44" s="26" t="s">
-        <v>131</v>
+      <c r="C44" s="12" t="s">
+        <v>130</v>
       </c>
       <c r="D44" s="5" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="E44" s="5" t="s">
         <v>108</v>
@@ -2132,11 +2129,11 @@
       <c r="B45" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C45" s="26" t="s">
-        <v>131</v>
+      <c r="C45" s="12" t="s">
+        <v>130</v>
       </c>
       <c r="D45" s="5" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="E45" s="5" t="s">
         <v>108</v>
@@ -2148,33 +2145,33 @@
       <c r="B46" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="C46" s="26" t="s">
+      <c r="C46" s="12" t="s">
+        <v>131</v>
+      </c>
+      <c r="D46" s="25" t="s">
         <v>132</v>
       </c>
-      <c r="D46" s="22" t="s">
-        <v>133</v>
-      </c>
-      <c r="E46" s="23"/>
+      <c r="E46" s="27"/>
       <c r="F46" s="5"/>
     </row>
     <row r="47" spans="1:6" ht="85" x14ac:dyDescent="0.2">
       <c r="A47" s="16" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B47" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C47" s="30" t="s">
-        <v>195</v>
+      <c r="C47" s="28" t="s">
+        <v>191</v>
       </c>
       <c r="D47" s="16" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="E47" s="16" t="s">
         <v>95</v>
       </c>
       <c r="F47" s="16" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="68" x14ac:dyDescent="0.2">
@@ -2182,7 +2179,7 @@
       <c r="B48" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C48" s="31"/>
+      <c r="C48" s="29"/>
       <c r="D48" s="17"/>
       <c r="E48" s="17"/>
       <c r="F48" s="17"/>
@@ -2192,29 +2189,29 @@
       <c r="B49" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C49" s="32"/>
+      <c r="C49" s="30"/>
       <c r="D49" s="18"/>
       <c r="E49" s="18"/>
       <c r="F49" s="18"/>
     </row>
     <row r="50" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A50" s="8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B50" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C50" s="33" t="s">
-        <v>137</v>
+      <c r="C50" s="22" t="s">
+        <v>136</v>
       </c>
       <c r="D50" s="19" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E50" s="19" t="s">
         <v>88</v>
       </c>
       <c r="F50" s="19" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="51" spans="1:6" ht="34" x14ac:dyDescent="0.2">
@@ -2222,7 +2219,7 @@
       <c r="B51" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C51" s="34"/>
+      <c r="C51" s="23"/>
       <c r="D51" s="20"/>
       <c r="E51" s="20"/>
       <c r="F51" s="20"/>
@@ -2232,7 +2229,7 @@
       <c r="B52" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C52" s="34"/>
+      <c r="C52" s="23"/>
       <c r="D52" s="20"/>
       <c r="E52" s="20"/>
       <c r="F52" s="20"/>
@@ -2242,7 +2239,7 @@
       <c r="B53" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C53" s="34"/>
+      <c r="C53" s="23"/>
       <c r="D53" s="20"/>
       <c r="E53" s="20"/>
       <c r="F53" s="20"/>
@@ -2252,7 +2249,7 @@
       <c r="B54" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C54" s="34"/>
+      <c r="C54" s="23"/>
       <c r="D54" s="20"/>
       <c r="E54" s="20"/>
       <c r="F54" s="20"/>
@@ -2262,23 +2259,23 @@
       <c r="B55" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C55" s="35"/>
+      <c r="C55" s="24"/>
       <c r="D55" s="21"/>
       <c r="E55" s="21"/>
       <c r="F55" s="21"/>
     </row>
     <row r="56" spans="1:6" ht="204" x14ac:dyDescent="0.2">
       <c r="A56" s="16" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B56" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="C56" s="28" t="s">
-        <v>142</v>
+      <c r="C56" s="14" t="s">
+        <v>141</v>
       </c>
       <c r="D56" s="7" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E56" s="7" t="s">
         <v>91</v>
@@ -2290,11 +2287,11 @@
       <c r="B57" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C57" s="28" t="s">
-        <v>143</v>
+      <c r="C57" s="14" t="s">
+        <v>210</v>
       </c>
       <c r="D57" s="7" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E57" s="7" t="s">
         <v>108</v>
@@ -2303,16 +2300,16 @@
     </row>
     <row r="58" spans="1:6" ht="204" x14ac:dyDescent="0.2">
       <c r="A58" s="19" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="B58" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C58" s="26" t="s">
-        <v>178</v>
+      <c r="C58" s="12" t="s">
+        <v>174</v>
       </c>
       <c r="D58" s="5" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="E58" s="5" t="s">
         <v>91</v>
@@ -2324,11 +2321,11 @@
       <c r="B59" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="C59" s="26" t="s">
-        <v>179</v>
+      <c r="C59" s="12" t="s">
+        <v>175</v>
       </c>
       <c r="D59" s="5" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="E59" s="5" t="s">
         <v>91</v>
@@ -2340,11 +2337,11 @@
       <c r="B60" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C60" s="26" t="s">
-        <v>180</v>
+      <c r="C60" s="12" t="s">
+        <v>176</v>
       </c>
       <c r="D60" s="5" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E60" s="5" t="s">
         <v>91</v>
@@ -2356,11 +2353,11 @@
       <c r="B61" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C61" s="26" t="s">
-        <v>181</v>
+      <c r="C61" s="12" t="s">
+        <v>177</v>
       </c>
       <c r="D61" s="5" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E61" s="5" t="s">
         <v>91</v>
@@ -2369,16 +2366,16 @@
     </row>
     <row r="62" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A62" s="16" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="B62" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="C62" s="28" t="s">
-        <v>185</v>
+      <c r="C62" s="14" t="s">
+        <v>181</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="E62" s="7" t="s">
         <v>108</v>
@@ -2390,11 +2387,11 @@
       <c r="B63" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="C63" s="28" t="s">
+      <c r="C63" s="14" t="s">
         <v>95</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="E63" s="7" t="s">
         <v>95</v>
@@ -2403,19 +2400,19 @@
     </row>
     <row r="64" spans="1:6" ht="68" x14ac:dyDescent="0.2">
       <c r="A64" s="19" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C64" s="33" t="s">
-        <v>194</v>
+      <c r="C64" s="22" t="s">
+        <v>190</v>
       </c>
       <c r="D64" s="5" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="F64" s="5"/>
     </row>
@@ -2424,12 +2421,12 @@
       <c r="B65" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="C65" s="34"/>
+      <c r="C65" s="23"/>
       <c r="D65" s="5" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="F65" s="5"/>
     </row>
@@ -2438,12 +2435,12 @@
       <c r="B66" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C66" s="34"/>
+      <c r="C66" s="23"/>
       <c r="D66" s="5" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="F66" s="5"/>
     </row>
@@ -2452,12 +2449,12 @@
       <c r="B67" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="C67" s="34"/>
+      <c r="C67" s="23"/>
       <c r="D67" s="5" t="s">
+        <v>185</v>
+      </c>
+      <c r="E67" s="5" t="s">
         <v>189</v>
-      </c>
-      <c r="E67" s="5" t="s">
-        <v>193</v>
       </c>
       <c r="F67" s="5"/>
     </row>
@@ -2466,12 +2463,12 @@
       <c r="B68" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C68" s="34"/>
+      <c r="C68" s="23"/>
       <c r="D68" s="5" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="F68" s="5"/>
     </row>
@@ -2480,12 +2477,12 @@
       <c r="B69" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C69" s="34"/>
+      <c r="C69" s="23"/>
       <c r="D69" s="5" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="F69" s="5"/>
     </row>
@@ -2494,12 +2491,12 @@
       <c r="B70" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C70" s="34"/>
+      <c r="C70" s="23"/>
       <c r="D70" s="5" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="F70" s="5"/>
     </row>
@@ -2508,40 +2505,40 @@
       <c r="B71" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C71" s="34"/>
-      <c r="D71" s="22" t="s">
+      <c r="C71" s="23"/>
+      <c r="D71" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="E71" s="24"/>
-      <c r="F71" s="23"/>
+      <c r="E71" s="26"/>
+      <c r="F71" s="27"/>
     </row>
     <row r="72" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A72" s="21"/>
       <c r="B72" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C72" s="35"/>
-      <c r="D72" s="22" t="s">
+      <c r="C72" s="24"/>
+      <c r="D72" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="E72" s="24"/>
-      <c r="F72" s="23"/>
+      <c r="E72" s="26"/>
+      <c r="F72" s="27"/>
     </row>
     <row r="73" spans="1:6" ht="85" x14ac:dyDescent="0.2">
       <c r="A73" s="16" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="B73" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="C73" s="30" t="s">
-        <v>196</v>
+      <c r="C73" s="28" t="s">
+        <v>192</v>
       </c>
       <c r="D73" s="16" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="E73" s="16" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="F73" s="16"/>
     </row>
@@ -2550,7 +2547,7 @@
       <c r="B74" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="C74" s="31"/>
+      <c r="C74" s="29"/>
       <c r="D74" s="17"/>
       <c r="E74" s="17"/>
       <c r="F74" s="17"/>
@@ -2560,7 +2557,7 @@
       <c r="B75" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="C75" s="32"/>
+      <c r="C75" s="30"/>
       <c r="D75" s="18"/>
       <c r="E75" s="18"/>
       <c r="F75" s="18"/>
@@ -2570,11 +2567,11 @@
       <c r="B76" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="C76" s="28" t="s">
-        <v>178</v>
+      <c r="C76" s="14" t="s">
+        <v>174</v>
       </c>
       <c r="D76" s="7" t="s">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="E76" s="7" t="s">
         <v>91</v>
@@ -2586,11 +2583,11 @@
       <c r="B77" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="C77" s="28" t="s">
-        <v>179</v>
+      <c r="C77" s="14" t="s">
+        <v>175</v>
       </c>
       <c r="D77" s="7" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="E77" s="7" t="s">
         <v>91</v>
@@ -2602,11 +2599,11 @@
       <c r="B78" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="C78" s="28" t="s">
-        <v>181</v>
+      <c r="C78" s="14" t="s">
+        <v>177</v>
       </c>
       <c r="D78" s="7" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="E78" s="7" t="s">
         <v>91</v>
@@ -2615,19 +2612,19 @@
     </row>
     <row r="79" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A79" s="19" t="s">
-        <v>203</v>
+        <v>199</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C79" s="33" t="s">
-        <v>194</v>
+      <c r="C79" s="22" t="s">
+        <v>190</v>
       </c>
       <c r="D79" s="5" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="F79" s="5"/>
     </row>
@@ -2636,12 +2633,12 @@
       <c r="B80" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C80" s="34"/>
+      <c r="C80" s="23"/>
       <c r="D80" s="5" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="F80" s="5"/>
     </row>
@@ -2650,12 +2647,12 @@
       <c r="B81" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="C81" s="34"/>
+      <c r="C81" s="23"/>
       <c r="D81" s="5" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="F81" s="5"/>
     </row>
@@ -2664,12 +2661,12 @@
       <c r="B82" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="C82" s="34"/>
+      <c r="C82" s="23"/>
       <c r="D82" s="5" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="F82" s="5"/>
     </row>
@@ -2678,12 +2675,12 @@
       <c r="B83" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C83" s="34"/>
+      <c r="C83" s="23"/>
       <c r="D83" s="5" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="F83" s="5"/>
     </row>
@@ -2692,12 +2689,12 @@
       <c r="B84" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="C84" s="34"/>
+      <c r="C84" s="23"/>
       <c r="D84" s="5" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="F84" s="5"/>
     </row>
@@ -2706,12 +2703,12 @@
       <c r="B85" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="C85" s="34"/>
+      <c r="C85" s="23"/>
       <c r="D85" s="5" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="F85" s="5"/>
     </row>
@@ -2720,51 +2717,58 @@
       <c r="B86" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C86" s="34"/>
-      <c r="D86" s="22" t="s">
+      <c r="C86" s="23"/>
+      <c r="D86" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="E86" s="24"/>
-      <c r="F86" s="23"/>
+      <c r="E86" s="26"/>
+      <c r="F86" s="27"/>
     </row>
     <row r="87" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A87" s="21"/>
       <c r="B87" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C87" s="35"/>
-      <c r="D87" s="22" t="s">
+      <c r="C87" s="24"/>
+      <c r="D87" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="E87" s="24"/>
-      <c r="F87" s="23"/>
+      <c r="E87" s="26"/>
+      <c r="F87" s="27"/>
     </row>
     <row r="88" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A88" s="7" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="B88" s="7" t="s">
         <v>81</v>
       </c>
-      <c r="C88" s="28" t="s">
-        <v>212</v>
+      <c r="C88" s="14" t="s">
+        <v>208</v>
       </c>
       <c r="D88" s="7" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="E88" s="7" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="F88" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="35">
-    <mergeCell ref="F73:F75"/>
-    <mergeCell ref="A73:A78"/>
-    <mergeCell ref="A79:A87"/>
-    <mergeCell ref="C79:C87"/>
-    <mergeCell ref="D86:F86"/>
-    <mergeCell ref="D87:F87"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="A2:A22"/>
+    <mergeCell ref="C27:C29"/>
+    <mergeCell ref="D27:D29"/>
+    <mergeCell ref="E27:E29"/>
+    <mergeCell ref="A23:A29"/>
+    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="E47:E49"/>
+    <mergeCell ref="C47:C49"/>
+    <mergeCell ref="A47:A49"/>
+    <mergeCell ref="C73:C75"/>
+    <mergeCell ref="D73:D75"/>
+    <mergeCell ref="E73:E75"/>
     <mergeCell ref="F27:F29"/>
     <mergeCell ref="A56:A57"/>
     <mergeCell ref="A58:A61"/>
@@ -2781,19 +2785,12 @@
     <mergeCell ref="D71:F71"/>
     <mergeCell ref="D72:F72"/>
     <mergeCell ref="D47:D49"/>
-    <mergeCell ref="E47:E49"/>
-    <mergeCell ref="C47:C49"/>
-    <mergeCell ref="A47:A49"/>
-    <mergeCell ref="C73:C75"/>
-    <mergeCell ref="D73:D75"/>
-    <mergeCell ref="E73:E75"/>
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="A2:A22"/>
-    <mergeCell ref="C27:C29"/>
-    <mergeCell ref="D27:D29"/>
-    <mergeCell ref="E27:E29"/>
-    <mergeCell ref="A23:A29"/>
-    <mergeCell ref="D26:E26"/>
+    <mergeCell ref="F73:F75"/>
+    <mergeCell ref="A73:A78"/>
+    <mergeCell ref="A79:A87"/>
+    <mergeCell ref="C79:C87"/>
+    <mergeCell ref="D86:F86"/>
+    <mergeCell ref="D87:F87"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/surveyProcessing.xlsx
+++ b/surveyProcessing.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10419"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamilajanmohamed/Library/CloudStorage/Dropbox/Research/ExpenseShocks/data/documentation/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kamilajanmohamed/Library/CloudStorage/Dropbox/Research/ExpenseShocks/code/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{916FC0BA-C15F-0C4C-B679-DA719F87C806}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ABA875C6-81B4-FB4E-A46B-C4228F732B90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1240" yWindow="0" windowWidth="27560" windowHeight="18000" xr2:uid="{57E50125-87C9-E840-AC46-56F2E007DB73}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{57E50125-87C9-E840-AC46-56F2E007DB73}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="213">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="221">
   <si>
     <t>Time Started</t>
   </si>
@@ -809,6 +809,33 @@
   </si>
   <si>
     <t>any_shock</t>
+  </si>
+  <si>
+    <t>Additional variables created ex post</t>
+  </si>
+  <si>
+    <t>lshock_hh_inc_annual</t>
+  </si>
+  <si>
+    <t>lshock_hh_inc_conflict</t>
+  </si>
+  <si>
+    <t>12*lshock_hh_inc</t>
+  </si>
+  <si>
+    <t>lshock_hh_inc_annual assigned to the same income bins as in the numerator-reported income</t>
+  </si>
+  <si>
+    <t>factor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lshock_hh_inc_bin_annual </t>
+  </si>
+  <si>
+    <t>Underreporeted monthly: lshock_hh_inc_bin_annual &lt; income
+Overreported monthly: lshock_hh_inc_bin_annual &gt; income
+No conflict: lshock_hh_inc_bin_annual == income
+NA: no monthly income reported/no annual income reported</t>
   </si>
 </sst>
 </file>
@@ -864,7 +891,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -961,11 +988,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -1012,6 +1048,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1021,6 +1075,15 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1042,37 +1105,16 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1409,7 +1451,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D15B38EE-C9F5-1649-922E-FE83B748618C}">
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:G91"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12" style="3" bestFit="1" customWidth="1"/>
@@ -1442,21 +1484,21 @@
       </c>
     </row>
     <row r="2" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="17" t="s">
         <v>123</v>
       </c>
       <c r="B2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="31" t="s">
+      <c r="C2" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="D2" s="31"/>
-      <c r="E2" s="31"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
       <c r="F2" s="5"/>
     </row>
     <row r="3" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A3" s="32"/>
+      <c r="A3" s="17"/>
       <c r="B3" s="5" t="s">
         <v>1</v>
       </c>
@@ -1472,7 +1514,7 @@
       <c r="F3" s="5"/>
     </row>
     <row r="4" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A4" s="32"/>
+      <c r="A4" s="17"/>
       <c r="B4" s="5" t="s">
         <v>2</v>
       </c>
@@ -1488,7 +1530,7 @@
       <c r="F4" s="5"/>
     </row>
     <row r="5" spans="1:7" ht="136" x14ac:dyDescent="0.2">
-      <c r="A5" s="32"/>
+      <c r="A5" s="17"/>
       <c r="B5" s="5" t="s">
         <v>3</v>
       </c>
@@ -1504,7 +1546,7 @@
       <c r="F5" s="5"/>
     </row>
     <row r="6" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A6" s="32"/>
+      <c r="A6" s="17"/>
       <c r="B6" s="5" t="s">
         <v>4</v>
       </c>
@@ -1520,7 +1562,7 @@
       <c r="F6" s="5"/>
     </row>
     <row r="7" spans="1:7" ht="85" x14ac:dyDescent="0.2">
-      <c r="A7" s="32"/>
+      <c r="A7" s="17"/>
       <c r="B7" s="5" t="s">
         <v>5</v>
       </c>
@@ -1536,7 +1578,7 @@
       <c r="F7" s="5"/>
     </row>
     <row r="8" spans="1:7" ht="153" x14ac:dyDescent="0.2">
-      <c r="A8" s="32"/>
+      <c r="A8" s="17"/>
       <c r="B8" s="5" t="s">
         <v>6</v>
       </c>
@@ -1552,7 +1594,7 @@
       <c r="F8" s="5"/>
     </row>
     <row r="9" spans="1:7" ht="102" x14ac:dyDescent="0.2">
-      <c r="A9" s="32"/>
+      <c r="A9" s="17"/>
       <c r="B9" s="5" t="s">
         <v>7</v>
       </c>
@@ -1568,7 +1610,7 @@
       <c r="F9" s="5"/>
     </row>
     <row r="10" spans="1:7" ht="68" x14ac:dyDescent="0.2">
-      <c r="A10" s="32"/>
+      <c r="A10" s="17"/>
       <c r="B10" s="5" t="s">
         <v>8</v>
       </c>
@@ -1584,7 +1626,7 @@
       <c r="F10" s="5"/>
     </row>
     <row r="11" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A11" s="32"/>
+      <c r="A11" s="17"/>
       <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
@@ -1600,7 +1642,7 @@
       <c r="F11" s="5"/>
     </row>
     <row r="12" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A12" s="32"/>
+      <c r="A12" s="17"/>
       <c r="B12" s="5" t="s">
         <v>10</v>
       </c>
@@ -1616,7 +1658,7 @@
       <c r="F12" s="5"/>
     </row>
     <row r="13" spans="1:7" ht="136" x14ac:dyDescent="0.2">
-      <c r="A13" s="32"/>
+      <c r="A13" s="17"/>
       <c r="B13" s="5" t="s">
         <v>11</v>
       </c>
@@ -1632,7 +1674,7 @@
       <c r="F13" s="5"/>
     </row>
     <row r="14" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A14" s="32"/>
+      <c r="A14" s="17"/>
       <c r="B14" s="6" t="s">
         <v>12</v>
       </c>
@@ -1649,7 +1691,7 @@
       <c r="G14" s="4"/>
     </row>
     <row r="15" spans="1:7" ht="119" x14ac:dyDescent="0.2">
-      <c r="A15" s="32"/>
+      <c r="A15" s="17"/>
       <c r="B15" s="5" t="s">
         <v>13</v>
       </c>
@@ -1665,7 +1707,7 @@
       <c r="F15" s="5"/>
     </row>
     <row r="16" spans="1:7" ht="17" x14ac:dyDescent="0.2">
-      <c r="A16" s="32"/>
+      <c r="A16" s="17"/>
       <c r="B16" s="5" t="s">
         <v>14</v>
       </c>
@@ -1681,7 +1723,7 @@
       <c r="F16" s="5"/>
     </row>
     <row r="17" spans="1:6" ht="170" x14ac:dyDescent="0.2">
-      <c r="A17" s="32"/>
+      <c r="A17" s="17"/>
       <c r="B17" s="5" t="s">
         <v>15</v>
       </c>
@@ -1697,7 +1739,7 @@
       <c r="F17" s="5"/>
     </row>
     <row r="18" spans="1:6" ht="85" x14ac:dyDescent="0.2">
-      <c r="A18" s="32"/>
+      <c r="A18" s="17"/>
       <c r="B18" s="5" t="s">
         <v>16</v>
       </c>
@@ -1713,7 +1755,7 @@
       <c r="F18" s="5"/>
     </row>
     <row r="19" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A19" s="32"/>
+      <c r="A19" s="17"/>
       <c r="B19" s="5" t="s">
         <v>17</v>
       </c>
@@ -1729,7 +1771,7 @@
       <c r="F19" s="5"/>
     </row>
     <row r="20" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A20" s="32"/>
+      <c r="A20" s="17"/>
       <c r="B20" s="5" t="s">
         <v>18</v>
       </c>
@@ -1747,7 +1789,7 @@
       </c>
     </row>
     <row r="21" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A21" s="32"/>
+      <c r="A21" s="17"/>
       <c r="B21" s="5" t="s">
         <v>19</v>
       </c>
@@ -1763,7 +1805,7 @@
       <c r="F21" s="5"/>
     </row>
     <row r="22" spans="1:6" ht="17" x14ac:dyDescent="0.2">
-      <c r="A22" s="32"/>
+      <c r="A22" s="17"/>
       <c r="B22" s="5" t="s">
         <v>20</v>
       </c>
@@ -1779,7 +1821,7 @@
       <c r="F22" s="5"/>
     </row>
     <row r="23" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A23" s="34" t="s">
+      <c r="A23" s="19" t="s">
         <v>128</v>
       </c>
       <c r="B23" s="7" t="s">
@@ -1797,7 +1839,7 @@
       <c r="F23" s="7"/>
     </row>
     <row r="24" spans="1:6" ht="119" x14ac:dyDescent="0.2">
-      <c r="A24" s="34"/>
+      <c r="A24" s="19"/>
       <c r="B24" s="7" t="s">
         <v>22</v>
       </c>
@@ -1813,7 +1855,7 @@
       <c r="F24" s="7"/>
     </row>
     <row r="25" spans="1:6" ht="409.6" x14ac:dyDescent="0.2">
-      <c r="A25" s="34"/>
+      <c r="A25" s="19"/>
       <c r="B25" s="7" t="s">
         <v>23</v>
       </c>
@@ -1829,59 +1871,59 @@
       <c r="F25" s="7"/>
     </row>
     <row r="26" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A26" s="34"/>
+      <c r="A26" s="19"/>
       <c r="B26" s="7" t="s">
         <v>24</v>
       </c>
       <c r="C26" s="14" t="s">
         <v>125</v>
       </c>
-      <c r="D26" s="35" t="s">
+      <c r="D26" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="E26" s="36"/>
+      <c r="E26" s="21"/>
       <c r="F26" s="7"/>
     </row>
     <row r="27" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A27" s="34"/>
+      <c r="A27" s="19"/>
       <c r="B27" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="C27" s="33" t="s">
+      <c r="C27" s="18" t="s">
         <v>138</v>
       </c>
-      <c r="D27" s="34" t="s">
+      <c r="D27" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="E27" s="34" t="s">
+      <c r="E27" s="19" t="s">
         <v>95</v>
       </c>
-      <c r="F27" s="16" t="s">
+      <c r="F27" s="22" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="28" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A28" s="34"/>
+      <c r="A28" s="19"/>
       <c r="B28" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="C28" s="33"/>
-      <c r="D28" s="34"/>
-      <c r="E28" s="34"/>
-      <c r="F28" s="17"/>
+      <c r="C28" s="18"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="23"/>
     </row>
     <row r="29" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A29" s="34"/>
+      <c r="A29" s="19"/>
       <c r="B29" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="C29" s="33"/>
-      <c r="D29" s="34"/>
-      <c r="E29" s="34"/>
-      <c r="F29" s="18"/>
+      <c r="C29" s="18"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="24"/>
     </row>
     <row r="30" spans="1:6" ht="119" x14ac:dyDescent="0.2">
-      <c r="A30" s="19" t="s">
+      <c r="A30" s="28" t="s">
         <v>129</v>
       </c>
       <c r="B30" s="5" t="s">
@@ -1899,7 +1941,7 @@
       <c r="F30" s="5"/>
     </row>
     <row r="31" spans="1:6" ht="187" x14ac:dyDescent="0.2">
-      <c r="A31" s="20"/>
+      <c r="A31" s="29"/>
       <c r="B31" s="5" t="s">
         <v>29</v>
       </c>
@@ -1915,7 +1957,7 @@
       <c r="F31" s="5"/>
     </row>
     <row r="32" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A32" s="20"/>
+      <c r="A32" s="29"/>
       <c r="B32" s="5" t="s">
         <v>30</v>
       </c>
@@ -1931,7 +1973,7 @@
       <c r="F32" s="5"/>
     </row>
     <row r="33" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A33" s="20"/>
+      <c r="A33" s="29"/>
       <c r="B33" s="5" t="s">
         <v>31</v>
       </c>
@@ -1947,7 +1989,7 @@
       <c r="F33" s="5"/>
     </row>
     <row r="34" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A34" s="20"/>
+      <c r="A34" s="29"/>
       <c r="B34" s="5" t="s">
         <v>32</v>
       </c>
@@ -1963,7 +2005,7 @@
       <c r="F34" s="5"/>
     </row>
     <row r="35" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A35" s="20"/>
+      <c r="A35" s="29"/>
       <c r="B35" s="5" t="s">
         <v>33</v>
       </c>
@@ -1979,7 +2021,7 @@
       <c r="F35" s="5"/>
     </row>
     <row r="36" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A36" s="20"/>
+      <c r="A36" s="29"/>
       <c r="B36" s="5" t="s">
         <v>34</v>
       </c>
@@ -1995,7 +2037,7 @@
       <c r="F36" s="5"/>
     </row>
     <row r="37" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A37" s="20"/>
+      <c r="A37" s="29"/>
       <c r="B37" s="5" t="s">
         <v>35</v>
       </c>
@@ -2011,7 +2053,7 @@
       <c r="F37" s="5"/>
     </row>
     <row r="38" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A38" s="20"/>
+      <c r="A38" s="29"/>
       <c r="B38" s="5" t="s">
         <v>36</v>
       </c>
@@ -2027,7 +2069,7 @@
       <c r="F38" s="5"/>
     </row>
     <row r="39" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A39" s="20"/>
+      <c r="A39" s="29"/>
       <c r="B39" s="5" t="s">
         <v>37</v>
       </c>
@@ -2045,7 +2087,7 @@
       </c>
     </row>
     <row r="40" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A40" s="20"/>
+      <c r="A40" s="29"/>
       <c r="B40" s="5" t="s">
         <v>38</v>
       </c>
@@ -2061,7 +2103,7 @@
       <c r="F40" s="5"/>
     </row>
     <row r="41" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A41" s="20"/>
+      <c r="A41" s="29"/>
       <c r="B41" s="5" t="s">
         <v>39</v>
       </c>
@@ -2077,7 +2119,7 @@
       <c r="F41" s="5"/>
     </row>
     <row r="42" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A42" s="20"/>
+      <c r="A42" s="29"/>
       <c r="B42" s="5" t="s">
         <v>40</v>
       </c>
@@ -2093,7 +2135,7 @@
       <c r="F42" s="5"/>
     </row>
     <row r="43" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A43" s="20"/>
+      <c r="A43" s="29"/>
       <c r="B43" s="5" t="s">
         <v>41</v>
       </c>
@@ -2109,7 +2151,7 @@
       <c r="F43" s="5"/>
     </row>
     <row r="44" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A44" s="20"/>
+      <c r="A44" s="29"/>
       <c r="B44" s="5" t="s">
         <v>42</v>
       </c>
@@ -2125,7 +2167,7 @@
       <c r="F44" s="5"/>
     </row>
     <row r="45" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A45" s="20"/>
+      <c r="A45" s="29"/>
       <c r="B45" s="5" t="s">
         <v>43</v>
       </c>
@@ -2141,58 +2183,58 @@
       <c r="F45" s="5"/>
     </row>
     <row r="46" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A46" s="21"/>
+      <c r="A46" s="30"/>
       <c r="B46" s="5" t="s">
         <v>42</v>
       </c>
       <c r="C46" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="D46" s="25" t="s">
+      <c r="D46" s="34" t="s">
         <v>132</v>
       </c>
-      <c r="E46" s="27"/>
+      <c r="E46" s="35"/>
       <c r="F46" s="5"/>
     </row>
     <row r="47" spans="1:6" ht="85" x14ac:dyDescent="0.2">
-      <c r="A47" s="16" t="s">
+      <c r="A47" s="22" t="s">
         <v>133</v>
       </c>
       <c r="B47" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="C47" s="28" t="s">
+      <c r="C47" s="25" t="s">
         <v>191</v>
       </c>
-      <c r="D47" s="16" t="s">
+      <c r="D47" s="22" t="s">
         <v>160</v>
       </c>
-      <c r="E47" s="16" t="s">
+      <c r="E47" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="F47" s="16" t="s">
+      <c r="F47" s="22" t="s">
         <v>161</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A48" s="17"/>
+      <c r="A48" s="23"/>
       <c r="B48" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="C48" s="29"/>
-      <c r="D48" s="17"/>
-      <c r="E48" s="17"/>
-      <c r="F48" s="17"/>
+      <c r="C48" s="26"/>
+      <c r="D48" s="23"/>
+      <c r="E48" s="23"/>
+      <c r="F48" s="23"/>
     </row>
     <row r="49" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A49" s="18"/>
+      <c r="A49" s="24"/>
       <c r="B49" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C49" s="30"/>
-      <c r="D49" s="18"/>
-      <c r="E49" s="18"/>
-      <c r="F49" s="18"/>
+      <c r="C49" s="27"/>
+      <c r="D49" s="24"/>
+      <c r="E49" s="24"/>
+      <c r="F49" s="24"/>
     </row>
     <row r="50" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A50" s="8" t="s">
@@ -2201,16 +2243,16 @@
       <c r="B50" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C50" s="22" t="s">
+      <c r="C50" s="31" t="s">
         <v>136</v>
       </c>
-      <c r="D50" s="19" t="s">
+      <c r="D50" s="28" t="s">
         <v>162</v>
       </c>
-      <c r="E50" s="19" t="s">
+      <c r="E50" s="28" t="s">
         <v>88</v>
       </c>
-      <c r="F50" s="19" t="s">
+      <c r="F50" s="28" t="s">
         <v>137</v>
       </c>
     </row>
@@ -2219,53 +2261,53 @@
       <c r="B51" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C51" s="23"/>
-      <c r="D51" s="20"/>
-      <c r="E51" s="20"/>
-      <c r="F51" s="20"/>
+      <c r="C51" s="32"/>
+      <c r="D51" s="29"/>
+      <c r="E51" s="29"/>
+      <c r="F51" s="29"/>
     </row>
     <row r="52" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A52" s="9"/>
       <c r="B52" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C52" s="23"/>
-      <c r="D52" s="20"/>
-      <c r="E52" s="20"/>
-      <c r="F52" s="20"/>
+      <c r="C52" s="32"/>
+      <c r="D52" s="29"/>
+      <c r="E52" s="29"/>
+      <c r="F52" s="29"/>
     </row>
     <row r="53" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A53" s="9"/>
       <c r="B53" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C53" s="23"/>
-      <c r="D53" s="20"/>
-      <c r="E53" s="20"/>
-      <c r="F53" s="20"/>
+      <c r="C53" s="32"/>
+      <c r="D53" s="29"/>
+      <c r="E53" s="29"/>
+      <c r="F53" s="29"/>
     </row>
     <row r="54" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A54" s="9"/>
       <c r="B54" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C54" s="23"/>
-      <c r="D54" s="20"/>
-      <c r="E54" s="20"/>
-      <c r="F54" s="20"/>
+      <c r="C54" s="32"/>
+      <c r="D54" s="29"/>
+      <c r="E54" s="29"/>
+      <c r="F54" s="29"/>
     </row>
     <row r="55" spans="1:6" ht="34" x14ac:dyDescent="0.2">
       <c r="A55" s="10"/>
       <c r="B55" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="C55" s="24"/>
-      <c r="D55" s="21"/>
-      <c r="E55" s="21"/>
-      <c r="F55" s="21"/>
+      <c r="C55" s="33"/>
+      <c r="D55" s="30"/>
+      <c r="E55" s="30"/>
+      <c r="F55" s="30"/>
     </row>
     <row r="56" spans="1:6" ht="204" x14ac:dyDescent="0.2">
-      <c r="A56" s="16" t="s">
+      <c r="A56" s="22" t="s">
         <v>140</v>
       </c>
       <c r="B56" s="7" t="s">
@@ -2283,7 +2325,7 @@
       <c r="F56" s="7"/>
     </row>
     <row r="57" spans="1:6" ht="102" x14ac:dyDescent="0.2">
-      <c r="A57" s="18"/>
+      <c r="A57" s="24"/>
       <c r="B57" s="7" t="s">
         <v>50</v>
       </c>
@@ -2299,7 +2341,7 @@
       <c r="F57" s="7"/>
     </row>
     <row r="58" spans="1:6" ht="204" x14ac:dyDescent="0.2">
-      <c r="A58" s="19" t="s">
+      <c r="A58" s="28" t="s">
         <v>167</v>
       </c>
       <c r="B58" s="5" t="s">
@@ -2317,7 +2359,7 @@
       <c r="F58" s="5"/>
     </row>
     <row r="59" spans="1:6" ht="255" x14ac:dyDescent="0.2">
-      <c r="A59" s="20"/>
+      <c r="A59" s="29"/>
       <c r="B59" s="5" t="s">
         <v>52</v>
       </c>
@@ -2333,7 +2375,7 @@
       <c r="F59" s="5"/>
     </row>
     <row r="60" spans="1:6" ht="119" x14ac:dyDescent="0.2">
-      <c r="A60" s="20"/>
+      <c r="A60" s="29"/>
       <c r="B60" s="5" t="s">
         <v>53</v>
       </c>
@@ -2349,7 +2391,7 @@
       <c r="F60" s="5"/>
     </row>
     <row r="61" spans="1:6" ht="136" x14ac:dyDescent="0.2">
-      <c r="A61" s="21"/>
+      <c r="A61" s="30"/>
       <c r="B61" s="5" t="s">
         <v>54</v>
       </c>
@@ -2365,7 +2407,7 @@
       <c r="F61" s="5"/>
     </row>
     <row r="62" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A62" s="16" t="s">
+      <c r="A62" s="22" t="s">
         <v>168</v>
       </c>
       <c r="B62" s="7" t="s">
@@ -2383,7 +2425,7 @@
       <c r="F62" s="7"/>
     </row>
     <row r="63" spans="1:6" ht="34" x14ac:dyDescent="0.2">
-      <c r="A63" s="18"/>
+      <c r="A63" s="24"/>
       <c r="B63" s="7" t="s">
         <v>56</v>
       </c>
@@ -2399,13 +2441,13 @@
       <c r="F63" s="7"/>
     </row>
     <row r="64" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A64" s="19" t="s">
+      <c r="A64" s="28" t="s">
         <v>178</v>
       </c>
       <c r="B64" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="C64" s="22" t="s">
+      <c r="C64" s="31" t="s">
         <v>190</v>
       </c>
       <c r="D64" s="5" t="s">
@@ -2417,11 +2459,11 @@
       <c r="F64" s="5"/>
     </row>
     <row r="65" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A65" s="20"/>
+      <c r="A65" s="29"/>
       <c r="B65" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="C65" s="23"/>
+      <c r="C65" s="32"/>
       <c r="D65" s="5" t="s">
         <v>183</v>
       </c>
@@ -2431,11 +2473,11 @@
       <c r="F65" s="5"/>
     </row>
     <row r="66" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A66" s="20"/>
+      <c r="A66" s="29"/>
       <c r="B66" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C66" s="23"/>
+      <c r="C66" s="32"/>
       <c r="D66" s="5" t="s">
         <v>184</v>
       </c>
@@ -2445,11 +2487,11 @@
       <c r="F66" s="5"/>
     </row>
     <row r="67" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A67" s="20"/>
+      <c r="A67" s="29"/>
       <c r="B67" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="C67" s="23"/>
+      <c r="C67" s="32"/>
       <c r="D67" s="5" t="s">
         <v>185</v>
       </c>
@@ -2459,11 +2501,11 @@
       <c r="F67" s="5"/>
     </row>
     <row r="68" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A68" s="20"/>
+      <c r="A68" s="29"/>
       <c r="B68" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C68" s="23"/>
+      <c r="C68" s="32"/>
       <c r="D68" s="5" t="s">
         <v>186</v>
       </c>
@@ -2473,11 +2515,11 @@
       <c r="F68" s="5"/>
     </row>
     <row r="69" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A69" s="20"/>
+      <c r="A69" s="29"/>
       <c r="B69" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="C69" s="23"/>
+      <c r="C69" s="32"/>
       <c r="D69" s="5" t="s">
         <v>187</v>
       </c>
@@ -2487,11 +2529,11 @@
       <c r="F69" s="5"/>
     </row>
     <row r="70" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A70" s="20"/>
+      <c r="A70" s="29"/>
       <c r="B70" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C70" s="23"/>
+      <c r="C70" s="32"/>
       <c r="D70" s="5" t="s">
         <v>188</v>
       </c>
@@ -2501,69 +2543,69 @@
       <c r="F70" s="5"/>
     </row>
     <row r="71" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A71" s="20"/>
+      <c r="A71" s="29"/>
       <c r="B71" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C71" s="23"/>
-      <c r="D71" s="25" t="s">
+      <c r="C71" s="32"/>
+      <c r="D71" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="E71" s="26"/>
-      <c r="F71" s="27"/>
+      <c r="E71" s="36"/>
+      <c r="F71" s="35"/>
     </row>
     <row r="72" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A72" s="21"/>
+      <c r="A72" s="30"/>
       <c r="B72" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="C72" s="24"/>
-      <c r="D72" s="25" t="s">
+      <c r="C72" s="33"/>
+      <c r="D72" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="E72" s="26"/>
-      <c r="F72" s="27"/>
+      <c r="E72" s="36"/>
+      <c r="F72" s="35"/>
     </row>
     <row r="73" spans="1:6" ht="85" x14ac:dyDescent="0.2">
-      <c r="A73" s="16" t="s">
+      <c r="A73" s="22" t="s">
         <v>197</v>
       </c>
       <c r="B73" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="C73" s="28" t="s">
+      <c r="C73" s="25" t="s">
         <v>192</v>
       </c>
-      <c r="D73" s="16" t="s">
+      <c r="D73" s="22" t="s">
         <v>193</v>
       </c>
-      <c r="E73" s="16" t="s">
+      <c r="E73" s="22" t="s">
         <v>194</v>
       </c>
-      <c r="F73" s="16"/>
+      <c r="F73" s="22"/>
     </row>
     <row r="74" spans="1:6" ht="68" x14ac:dyDescent="0.2">
-      <c r="A74" s="17"/>
+      <c r="A74" s="23"/>
       <c r="B74" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="C74" s="29"/>
-      <c r="D74" s="17"/>
-      <c r="E74" s="17"/>
-      <c r="F74" s="17"/>
+      <c r="C74" s="26"/>
+      <c r="D74" s="23"/>
+      <c r="E74" s="23"/>
+      <c r="F74" s="23"/>
     </row>
     <row r="75" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A75" s="17"/>
+      <c r="A75" s="23"/>
       <c r="B75" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="C75" s="30"/>
-      <c r="D75" s="18"/>
-      <c r="E75" s="18"/>
-      <c r="F75" s="18"/>
+      <c r="C75" s="27"/>
+      <c r="D75" s="24"/>
+      <c r="E75" s="24"/>
+      <c r="F75" s="24"/>
     </row>
     <row r="76" spans="1:6" ht="204" x14ac:dyDescent="0.2">
-      <c r="A76" s="17"/>
+      <c r="A76" s="23"/>
       <c r="B76" s="7" t="s">
         <v>69</v>
       </c>
@@ -2579,7 +2621,7 @@
       <c r="F76" s="7"/>
     </row>
     <row r="77" spans="1:6" ht="255" x14ac:dyDescent="0.2">
-      <c r="A77" s="17"/>
+      <c r="A77" s="23"/>
       <c r="B77" s="7" t="s">
         <v>70</v>
       </c>
@@ -2595,7 +2637,7 @@
       <c r="F77" s="7"/>
     </row>
     <row r="78" spans="1:6" ht="136" x14ac:dyDescent="0.2">
-      <c r="A78" s="18"/>
+      <c r="A78" s="24"/>
       <c r="B78" s="7" t="s">
         <v>71</v>
       </c>
@@ -2611,13 +2653,13 @@
       <c r="F78" s="7"/>
     </row>
     <row r="79" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A79" s="19" t="s">
+      <c r="A79" s="28" t="s">
         <v>199</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C79" s="22" t="s">
+      <c r="C79" s="31" t="s">
         <v>190</v>
       </c>
       <c r="D79" s="5" t="s">
@@ -2629,11 +2671,11 @@
       <c r="F79" s="5"/>
     </row>
     <row r="80" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A80" s="20"/>
+      <c r="A80" s="29"/>
       <c r="B80" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C80" s="23"/>
+      <c r="C80" s="32"/>
       <c r="D80" s="5" t="s">
         <v>201</v>
       </c>
@@ -2643,11 +2685,11 @@
       <c r="F80" s="5"/>
     </row>
     <row r="81" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A81" s="20"/>
+      <c r="A81" s="29"/>
       <c r="B81" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="C81" s="23"/>
+      <c r="C81" s="32"/>
       <c r="D81" s="5" t="s">
         <v>202</v>
       </c>
@@ -2657,11 +2699,11 @@
       <c r="F81" s="5"/>
     </row>
     <row r="82" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A82" s="20"/>
+      <c r="A82" s="29"/>
       <c r="B82" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="C82" s="23"/>
+      <c r="C82" s="32"/>
       <c r="D82" s="5" t="s">
         <v>203</v>
       </c>
@@ -2671,11 +2713,11 @@
       <c r="F82" s="5"/>
     </row>
     <row r="83" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A83" s="20"/>
+      <c r="A83" s="29"/>
       <c r="B83" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="C83" s="23"/>
+      <c r="C83" s="32"/>
       <c r="D83" s="5" t="s">
         <v>204</v>
       </c>
@@ -2685,11 +2727,11 @@
       <c r="F83" s="5"/>
     </row>
     <row r="84" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A84" s="20"/>
+      <c r="A84" s="29"/>
       <c r="B84" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="C84" s="23"/>
+      <c r="C84" s="32"/>
       <c r="D84" s="5" t="s">
         <v>205</v>
       </c>
@@ -2699,11 +2741,11 @@
       <c r="F84" s="5"/>
     </row>
     <row r="85" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A85" s="20"/>
+      <c r="A85" s="29"/>
       <c r="B85" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="C85" s="23"/>
+      <c r="C85" s="32"/>
       <c r="D85" s="5" t="s">
         <v>206</v>
       </c>
@@ -2713,28 +2755,28 @@
       <c r="F85" s="5"/>
     </row>
     <row r="86" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A86" s="20"/>
+      <c r="A86" s="29"/>
       <c r="B86" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="C86" s="23"/>
-      <c r="D86" s="25" t="s">
+      <c r="C86" s="32"/>
+      <c r="D86" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="E86" s="26"/>
-      <c r="F86" s="27"/>
+      <c r="E86" s="36"/>
+      <c r="F86" s="35"/>
     </row>
     <row r="87" spans="1:6" ht="51" x14ac:dyDescent="0.2">
-      <c r="A87" s="21"/>
+      <c r="A87" s="30"/>
       <c r="B87" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C87" s="24"/>
-      <c r="D87" s="25" t="s">
+      <c r="C87" s="33"/>
+      <c r="D87" s="34" t="s">
         <v>85</v>
       </c>
-      <c r="E87" s="26"/>
-      <c r="F87" s="27"/>
+      <c r="E87" s="36"/>
+      <c r="F87" s="35"/>
     </row>
     <row r="88" spans="1:6" ht="51" x14ac:dyDescent="0.2">
       <c r="A88" s="7" t="s">
@@ -2754,21 +2796,53 @@
       </c>
       <c r="F88" s="7"/>
     </row>
+    <row r="89" spans="1:6" ht="68" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="38" t="s">
+        <v>213</v>
+      </c>
+      <c r="C89" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="D89" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="E89" s="3" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" ht="34" x14ac:dyDescent="0.2">
+      <c r="A90" s="37"/>
+      <c r="C90" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="D90" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="E90" s="3" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" ht="119" x14ac:dyDescent="0.2">
+      <c r="A91" s="37"/>
+      <c r="C91" s="15" t="s">
+        <v>220</v>
+      </c>
+      <c r="D91" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="E91" s="3" t="s">
+        <v>218</v>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="35">
-    <mergeCell ref="C2:E2"/>
-    <mergeCell ref="A2:A22"/>
-    <mergeCell ref="C27:C29"/>
-    <mergeCell ref="D27:D29"/>
-    <mergeCell ref="E27:E29"/>
-    <mergeCell ref="A23:A29"/>
-    <mergeCell ref="D26:E26"/>
-    <mergeCell ref="E47:E49"/>
-    <mergeCell ref="C47:C49"/>
-    <mergeCell ref="A47:A49"/>
-    <mergeCell ref="C73:C75"/>
-    <mergeCell ref="D73:D75"/>
-    <mergeCell ref="E73:E75"/>
+  <mergeCells count="36">
+    <mergeCell ref="A89:A91"/>
+    <mergeCell ref="F73:F75"/>
+    <mergeCell ref="A73:A78"/>
+    <mergeCell ref="A79:A87"/>
+    <mergeCell ref="C79:C87"/>
+    <mergeCell ref="D86:F86"/>
+    <mergeCell ref="D87:F87"/>
     <mergeCell ref="F27:F29"/>
     <mergeCell ref="A56:A57"/>
     <mergeCell ref="A58:A61"/>
@@ -2785,12 +2859,19 @@
     <mergeCell ref="D71:F71"/>
     <mergeCell ref="D72:F72"/>
     <mergeCell ref="D47:D49"/>
-    <mergeCell ref="F73:F75"/>
-    <mergeCell ref="A73:A78"/>
-    <mergeCell ref="A79:A87"/>
-    <mergeCell ref="C79:C87"/>
-    <mergeCell ref="D86:F86"/>
-    <mergeCell ref="D87:F87"/>
+    <mergeCell ref="E47:E49"/>
+    <mergeCell ref="C47:C49"/>
+    <mergeCell ref="A47:A49"/>
+    <mergeCell ref="C73:C75"/>
+    <mergeCell ref="D73:D75"/>
+    <mergeCell ref="E73:E75"/>
+    <mergeCell ref="C2:E2"/>
+    <mergeCell ref="A2:A22"/>
+    <mergeCell ref="C27:C29"/>
+    <mergeCell ref="D27:D29"/>
+    <mergeCell ref="E27:E29"/>
+    <mergeCell ref="A23:A29"/>
+    <mergeCell ref="D26:E26"/>
   </mergeCells>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
